--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,0</t>
+          <t>-1,07; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,65</t>
+          <t>0,53; 5,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,51</t>
+          <t>0,45; 2,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,19</t>
+          <t>0,36; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,5; 3,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; —</t>
+          <t>-6,73; —</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,86</t>
+          <t>1,3; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,05</t>
+          <t>0,82; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,93</t>
+          <t>-1,22; 3,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125,04; 2828,71</t>
+          <t>103,53; 3148,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,14; —</t>
+          <t>11,24; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 153,68</t>
+          <t>-29,12; 157,92</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,24</t>
+          <t>1,29; 6,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,09</t>
+          <t>1,44; 5,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 12,58</t>
+          <t>4,63; 11,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,45; 465,13</t>
+          <t>35,31; 490,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,33; 448,03</t>
+          <t>41,01; 415,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,69; 567,93</t>
+          <t>69,9; 508,74</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,45</t>
+          <t>7,41; 15,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,48</t>
+          <t>6,12; 14,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,6</t>
+          <t>5,72; 12,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152,14; 691,51</t>
+          <t>145,57; 712,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,33; 434,49</t>
+          <t>87,14; 417,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,91; 175,17</t>
+          <t>53,92; 172,37</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,47</t>
+          <t>-0,01; 11,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 19,52</t>
+          <t>9,69; 19,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 13,53</t>
+          <t>-6,53; 13,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 106,29</t>
+          <t>-0,57; 113,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103,14; 405,4</t>
+          <t>103,19; 415,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 113,04</t>
+          <t>-45,19; 112,08</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,17; 21,6</t>
+          <t>6,76; 21,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,43</t>
+          <t>2,89; 15,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 22,22</t>
+          <t>11,89; 23,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,72; 134,38</t>
+          <t>27,82; 133,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,73; 117,08</t>
+          <t>14,55; 116,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,65; 94,35</t>
+          <t>38,61; 100,06</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,86</t>
+          <t>4,57; 6,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,03</t>
+          <t>4,72; 7,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,97</t>
+          <t>4,63; 9,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111,2; 217,98</t>
+          <t>113,53; 227,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>132,22; 256,47</t>
+          <t>131,62; 257,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,6; 159,89</t>
+          <t>68,95; 162,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>341,78%</t>
+          <t>423,35%</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,65</t>
+          <t>0,47; 2,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,36</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,98</t>
+          <t>0,81; 4,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; —</t>
+          <t>10,79; —</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,05</t>
+          <t>1,1; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,2</t>
+          <t>0,81; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,01</t>
+          <t>-0,45; 3,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103,53; 3148,87</t>
+          <t>80,26; 2675,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,24; —</t>
+          <t>11,93; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 157,92</t>
+          <t>-13,72; 198,73</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,71</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>180,57%</t>
+          <t>103,91%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,29</t>
+          <t>1,67; 6,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,87</t>
+          <t>1,36; 5,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,63</t>
+          <t>3,14; 8,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,31; 490,87</t>
+          <t>46,66; 475,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,01; 415,56</t>
+          <t>35,94; 398,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,9; 508,74</t>
+          <t>41,8; 188,89</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103,15%</t>
+          <t>106,09%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 15,35</t>
+          <t>7,66; 15,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 14,04</t>
+          <t>5,94; 13,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,29</t>
+          <t>5,68; 12,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145,57; 712,71</t>
+          <t>150,36; 686,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,14; 417,28</t>
+          <t>87,1; 384,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,92; 172,37</t>
+          <t>53,73; 167,56</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>110,03%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 11,9</t>
+          <t>-0,41; 11,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 19,74</t>
+          <t>9,19; 19,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 13,63</t>
+          <t>9,25; 17,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 113,46</t>
+          <t>-4,07; 108,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103,19; 415,53</t>
+          <t>103,64; 409,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 112,08</t>
+          <t>61,86; 164,91</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,33</t>
+          <t>17,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 21,36</t>
+          <t>7,19; 21,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 15,79</t>
+          <t>2,7; 15,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 23,35</t>
+          <t>11,47; 22,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,82; 133,71</t>
+          <t>29,44; 139,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 116,66</t>
+          <t>14,03; 118,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,61; 100,06</t>
+          <t>38,14; 94,82</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109,25%</t>
+          <t>115,23%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,87</t>
+          <t>4,52; 7,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,08</t>
+          <t>4,67; 7,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,09</t>
+          <t>6,76; 9,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113,53; 227,32</t>
+          <t>108,48; 224,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>131,62; 257,54</t>
+          <t>132,91; 263,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,95; 162,33</t>
+          <t>88,99; 146,03</t>
         </is>
       </c>
     </row>
